--- a/docs/05-Power/PowerBudget.xlsx
+++ b/docs/05-Power/PowerBudget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksnha\Documents\Courses\EGR 314\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8836AD13-65BD-4427-AB81-760D13D41C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CC90AD-90C5-4168-8B06-A698BEF4FB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Budget" sheetId="1" r:id="rId1"/>
@@ -256,13 +256,13 @@
     <t>Battery (shared)</t>
   </si>
   <si>
-    <t>-12V</t>
-  </si>
-  <si>
     <t>120VAC</t>
   </si>
   <si>
     <t>BK-12W-T8</t>
+  </si>
+  <si>
+    <t>-9V</t>
   </si>
 </sst>
 </file>
@@ -722,20 +722,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -748,6 +737,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -762,17 +754,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1140,13 +1140,13 @@
       <c r="A1" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1211,16 +1211,16 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="67"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -1309,16 +1309,16 @@
       <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="71"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="72"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="67"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
@@ -1422,13 +1422,13 @@
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
       <c r="G18" s="14">
         <f>SUM(G13:G17)</f>
         <v>360</v>
@@ -1439,13 +1439,13 @@
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
       <c r="G19" s="22">
         <v>0.25</v>
       </c>
@@ -1453,13 +1453,13 @@
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
       <c r="G20" s="14">
         <f>G18*(1+G19)</f>
         <v>450</v>
@@ -1505,13 +1505,13 @@
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
       <c r="G23" s="26">
         <f>G22-G20</f>
         <v>550</v>
@@ -1531,38 +1531,38 @@
       <c r="H24" s="33"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="72"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="67"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="64"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="66"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="80"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="72"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="67"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
@@ -1598,10 +1598,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D29" s="54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>32</v>
@@ -1627,7 +1627,7 @@
       <c r="H30" s="39"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="68" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="52" t="s">
@@ -1654,7 +1654,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
       <c r="D32" s="12"/>
@@ -1664,7 +1664,7 @@
       <c r="H32" s="15"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
+      <c r="A33" s="69"/>
       <c r="B33" s="16"/>
       <c r="D33" s="12"/>
       <c r="E33" s="13"/>
@@ -1673,13 +1673,13 @@
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="38"/>
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
       <c r="G34" s="36">
         <f>G29-SUM(G31:G33)</f>
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>12</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E37" s="58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F37" s="59">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
       <c r="H38" s="39"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="68" t="s">
         <v>33</v>
       </c>
       <c r="B39" s="52" t="s">
@@ -1788,7 +1788,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="73"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="12"/>
@@ -1798,7 +1798,7 @@
       <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="73"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="16"/>
       <c r="D41" s="12"/>
       <c r="E41" s="13"/>
@@ -1807,13 +1807,13 @@
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="38"/>
-      <c r="B42" s="74" t="s">
+      <c r="B42" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
       <c r="G42" s="36">
         <f>G37-SUM(G39:G41)</f>
         <v>2000</v>
@@ -1891,7 +1891,7 @@
       <c r="H46" s="39"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="61" t="s">
+      <c r="A47" s="68" t="s">
         <v>33</v>
       </c>
       <c r="B47" s="52" t="s">
@@ -1918,7 +1918,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61"/>
+      <c r="A48" s="68"/>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
       <c r="D48" s="12"/>
@@ -1928,7 +1928,7 @@
       <c r="H48" s="15"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="61"/>
+      <c r="A49" s="68"/>
       <c r="B49" s="16"/>
       <c r="D49" s="12"/>
       <c r="E49" s="13"/>
@@ -1937,13 +1937,13 @@
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="38"/>
-      <c r="B50" s="62" t="s">
+      <c r="B50" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="C50" s="62"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="63"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="77"/>
       <c r="G50" s="36">
         <f>G45-SUM(G47:G49)</f>
         <v>800</v>
@@ -1963,14 +1963,14 @@
       <c r="H51" s="37"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="77"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="73"/>
       <c r="G52" s="42"/>
       <c r="H52" s="42"/>
     </row>
@@ -1989,7 +1989,7 @@
       <c r="F53" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="G53" s="82" t="s">
+      <c r="G53" s="61" t="s">
         <v>37</v>
       </c>
       <c r="H53" s="47"/>
@@ -2031,40 +2031,40 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="78" t="s">
+      <c r="A56" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="78"/>
-      <c r="C56" s="78"/>
-      <c r="D56" s="78"/>
-      <c r="E56" s="78"/>
-      <c r="F56" s="78"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="74"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
       <c r="G56" s="48"/>
       <c r="H56" s="48"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="67" t="s">
+      <c r="A57" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B58" s="69"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="69"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
